--- a/input/resources/source-data/DEQM_Capability_Statement_Reporter_Client.xlsx
+++ b/input/resources/source-data/DEQM_Capability_Statement_Reporter_Client.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\davinci-deqm\input\resources\source-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SourceControl\Git\HL7\davinci-deqm\input\resources\source-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547BDE7F-8133-4B37-855F-32D9BDB902EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FDB49A-44C9-4ADF-BADA-64AC2720B917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3312" yWindow="1020" windowWidth="26052" windowHeight="15240" activeTab="3" xr2:uid="{33C1B24A-521B-4A24-AA1F-999D8048322A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{33C1B24A-521B-4A24-AA1F-999D8048322A}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="11" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">profiles!$A$1:$D$11</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -475,34 +475,34 @@
     <t>For general security consideration refer to the [Security and Privacy Considerations](http://hl7.org/fhir/R4/secpriv-module.html).</t>
   </si>
   <si>
-    <t xml:space="preserve">Da Vinci DEQM Producer Client **SHALL** support at least one of the following  transactions defined in the *Framework* Section of  this  Implementation Guide:
+    <t>The DaVinci DEQM Reporter Client **SHALL** be capable of supporting at least one of the DEQM MeasureReport Profiles listed above and all the DEQM, CQFM and QI Core Profiles they reference.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/davinci-deqm/</t>
+  </si>
+  <si>
+    <t>3.1.0</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/davinci-deqm/ImplementationGuide/hl7.fhir.us.davinci-deqm|3.1.0</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/qicore/ImplementationGuide/hl7.fhir.us.qicore|4.1.0</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/cqfmeasures/ImplementationGuide/hl7.fhir.us.cqfmeasures|3.0.0</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization</t>
+  </si>
+  <si>
+    <t>QI Core Organization Profile</t>
+  </si>
+  <si>
+    <t>Da Vinci DEQM Producer Client **SHALL** support at least one of the following  transactions defined in the *Framework* Section of  this  Implementation Guide:
 - Individual Reporting
 - Summary Reporting
-</t>
-  </si>
-  <si>
-    <t>The DaVinci DEQM Reporter Client **SHALL** be capable of supporting at least one of the DEQM MeasureReport Profiles listed above and all the DEQM, CQFM and QI Core Profiles they reference.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/davinci-deqm/</t>
-  </si>
-  <si>
-    <t>3.1.0</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/davinci-deqm/ImplementationGuide/hl7.fhir.us.davinci-deqm|3.1.0</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/qicore/ImplementationGuide/hl7.fhir.us.qicore|4.1.0</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/cqfmeasures/ImplementationGuide/hl7.fhir.us.cqfmeasures|3.0.0</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization</t>
-  </si>
-  <si>
-    <t>QI Core Organization Profile</t>
+DEQM Producer Client **SHALL** support at least one of 'batch' or 'transaction'.</t>
   </si>
 </sst>
 </file>
@@ -590,7 +590,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -599,7 +599,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1"/>
@@ -623,9 +622,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -663,7 +662,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -769,7 +768,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -911,7 +910,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -920,9 +919,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFC67B7-00C2-40ED-8335-934B8B849BEB}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -930,7 +929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -938,7 +937,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -946,7 +945,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -954,15 +953,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>123</v>
       </c>
@@ -970,7 +969,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -978,7 +977,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -994,41 +993,41 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA7A46F-8381-432D-A5A2-CA05BE31957E}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1048,7 +1047,7 @@
       <c r="F2" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <f t="shared" ref="J2" si="1">"Fetches a bundle of all "&amp;B2&amp;" resources matching the specified "&amp;SUBSTITUTE(D2,","," and ")</f>
         <v>Fetches a bundle of all !Encounter resources matching the specified class and date</v>
       </c>
@@ -1061,13 +1060,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15F3286-55C1-40D0-93FC-C97EF26956B8}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="2" width="95.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="95.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1075,7 +1074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1083,15 +1082,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -1099,7 +1098,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1107,15 +1106,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1123,15 +1122,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1150,13 +1149,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0829A918-BBB6-6345-897C-371FBE4213DF}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="68.109375" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" customWidth="1"/>
+    <col min="2" max="2" width="68.140625" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1164,20 +1163,20 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>137</v>
+      <c r="B3" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1189,15 +1188,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B139EF60-0633-48C5-B394-C56F006BD6B3}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="98.44140625" customWidth="1"/>
-    <col min="2" max="2" width="60.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="98.42578125" customWidth="1"/>
+    <col min="2" max="2" width="60.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1211,7 +1210,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -1225,7 +1224,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>109</v>
       </c>
@@ -1239,7 +1238,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>110</v>
       </c>
@@ -1253,7 +1252,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -1267,7 +1266,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>112</v>
       </c>
@@ -1281,12 +1280,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" t="s">
         <v>138</v>
-      </c>
-      <c r="B7" t="s">
-        <v>139</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -1295,7 +1294,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -1309,7 +1308,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -1323,7 +1322,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>115</v>
       </c>
@@ -1347,19 +1346,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACB4CFA-AAEF-4FC6-A49B-107CEE80A317}">
   <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
     <col min="3" max="3" width="53" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="6" width="17.44140625" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -1417,23 +1416,23 @@
       <c r="S1" t="s">
         <v>103</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>107</v>
       </c>
       <c r="X1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="60.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -1441,7 +1440,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1457,15 +1456,15 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1491,14 +1490,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E2E280-092F-4777-8984-8212A8DAB750}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1506,7 +1505,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1514,22 +1513,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1537,12 +1536,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1550,12 +1549,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -1568,9 +1567,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B36F46D6-CA8E-44D2-B3D1-E2BF7BBCE19C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1581,16 +1580,16 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -1599,7 +1598,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>76</v>
       </c>
@@ -1608,7 +1607,7 @@
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -1625,21 +1624,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7399C2ED-EDEB-47AB-8C1E-1290512B1D2F}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="63.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" customWidth="1"/>
-    <col min="4" max="5" width="9.109375" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" customWidth="1"/>
-    <col min="8" max="8" width="34.6640625" customWidth="1"/>
-    <col min="9" max="15" width="9.109375" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" customWidth="1"/>
+    <col min="9" max="15" width="9.140625" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1692,7 +1691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
     </row>
   </sheetData>
